--- a/Pagina_WEB_-_Relación_de_Proveedores_e_Influencer_de_la_PH.xlsx
+++ b/Pagina_WEB_-_Relación_de_Proveedores_e_Influencer_de_la_PH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F780721F-F106-433B-88E6-9F5D4F0E3FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47189FF-6DC4-4BA0-8C3A-A001C96E566A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82BA444D-32AC-4ADB-8060-7C99B47ACAD6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
   <si>
     <t>CATEGORIA</t>
   </si>
@@ -171,9 +171,6 @@
     <t>William Piñeros D</t>
   </si>
   <si>
-    <t>Construccion</t>
-  </si>
-  <si>
     <t>apsandovalb</t>
   </si>
   <si>
@@ -349,6 +346,12 @@
   </si>
   <si>
     <t>Diana Paola Morales</t>
+  </si>
+  <si>
+    <t>ALIADO</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -756,945 +759,1022 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE12FBFD-9D11-4FAC-BCDD-CA1E61A848F7}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>3008005017</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>3017446570</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>3004059419</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>3207663189</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>3163659004</v>
       </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>3185163937</v>
       </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>3152086323</v>
       </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>3007771259</v>
       </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>3183746560</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>3164433586</v>
       </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>3219269921</v>
       </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>3219269921</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>3176934085</v>
       </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>3176839218</v>
       </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>3135424669</v>
       </c>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <v>3013989550</v>
       </c>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>3147702926</v>
       </c>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>3160100157</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3122798313</v>
+      </c>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3122798313</v>
-      </c>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="1">
+        <v>3148008632</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="1">
-        <v>3148008632</v>
-      </c>
-      <c r="E25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="1">
         <v>3136853351</v>
       </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="1"/>
+      <c r="F27" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="E28" s="1">
+        <v>3122021035</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="1">
-        <v>3122021035</v>
-      </c>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="E29" s="1">
+        <v>3225324129</v>
+      </c>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="1">
-        <v>3225324129</v>
-      </c>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E30" s="1">
+        <v>3118836109</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="1">
-        <v>3118836109</v>
-      </c>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="E31" s="1">
+        <v>3154866316</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="1">
-        <v>3154866316</v>
-      </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <v>3192455834</v>
       </c>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3178403593</v>
+      </c>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="1">
-        <v>3178403593</v>
-      </c>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="E36" s="1">
+        <v>3217058437</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3135424669</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="1">
-        <v>3217058437</v>
-      </c>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="E38" s="1">
+        <v>3173839231</v>
+      </c>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="1">
-        <v>3135424669</v>
-      </c>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3186992557</v>
+      </c>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="1">
-        <v>3173839231</v>
-      </c>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D39" s="1">
-        <v>3186992557</v>
-      </c>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="E40" s="1">
+        <v>3185098810</v>
+      </c>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="1">
-        <v>3185098810</v>
-      </c>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="E41" s="1">
+        <v>3113764066</v>
+      </c>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="1">
-        <v>3113764066</v>
-      </c>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="E42" s="1">
+        <v>3127274529</v>
+      </c>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D42" s="1">
-        <v>3127274529</v>
-      </c>
-      <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="E43" s="1">
+        <v>3173932197</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="1">
-        <v>3173932197</v>
-      </c>
-      <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="E44" s="1">
+        <v>3178452205</v>
+      </c>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="1">
-        <v>3178452205</v>
-      </c>
-      <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="E45" s="1">
+        <v>3002001004</v>
+      </c>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="1">
-        <v>3002001004</v>
-      </c>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="E46" s="1">
+        <v>3217072538</v>
+      </c>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="1">
-        <v>3217072538</v>
-      </c>
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="E47" s="1">
+        <v>3215136495</v>
+      </c>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D47" s="1">
-        <v>3215136495</v>
-      </c>
-      <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="E48" s="1">
+        <v>3133939882</v>
+      </c>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="1">
-        <v>3133939882</v>
-      </c>
-      <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="E49" s="1">
+        <v>3023477519</v>
+      </c>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="1">
-        <v>3023477519</v>
-      </c>
-      <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="E50" s="1">
+        <v>3207571725</v>
+      </c>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3168204847</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3168204847</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="1">
-        <v>3207571725</v>
-      </c>
-      <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="1" t="s">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="1">
-        <v>3168204847</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3168204847</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="E54" s="1"/>
+      <c r="F54" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E25" r:id="rId1" xr:uid="{FBE13389-DAC0-4EEE-BC9D-1BCB60BBD8CA}"/>
-    <hyperlink ref="E27" r:id="rId2" xr:uid="{85E27D7D-9BCF-4E8C-AD3D-E047AC3C7C33}"/>
-    <hyperlink ref="E51" r:id="rId3" xr:uid="{3E9B4088-98E9-48DA-8A90-DE94E44EDEBE}"/>
-    <hyperlink ref="E53" r:id="rId4" xr:uid="{E99C66E5-03F8-4A2A-AED5-928D12F0F01A}"/>
-    <hyperlink ref="E54" r:id="rId5" xr:uid="{0E7B096A-5C61-4B0B-AD1F-50A7BAF71B6B}"/>
+    <hyperlink ref="F25" r:id="rId1" xr:uid="{FBE13389-DAC0-4EEE-BC9D-1BCB60BBD8CA}"/>
+    <hyperlink ref="F27" r:id="rId2" xr:uid="{85E27D7D-9BCF-4E8C-AD3D-E047AC3C7C33}"/>
+    <hyperlink ref="F51" r:id="rId3" xr:uid="{3E9B4088-98E9-48DA-8A90-DE94E44EDEBE}"/>
+    <hyperlink ref="F53" r:id="rId4" xr:uid="{E99C66E5-03F8-4A2A-AED5-928D12F0F01A}"/>
+    <hyperlink ref="F54" r:id="rId5" xr:uid="{0E7B096A-5C61-4B0B-AD1F-50A7BAF71B6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,34 +1811,34 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
